--- a/output/20260401_MK_2026_DACH_Clipping_Report___Analysis.xlsx
+++ b/output/20260401_MK_2026_DACH_Clipping_Report___Analysis.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46113.41248261598</v>
+        <v>46113.66696186876</v>
       </c>
     </row>
     <row r="8">

--- a/output/20260401_MK_2026_DACH_Clipping_Report___Analysis.xlsx
+++ b/output/20260401_MK_2026_DACH_Clipping_Report___Analysis.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46113.66696186876</v>
+        <v>46113.84007773781</v>
       </c>
     </row>
     <row r="8">
